--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -9420,7 +9420,7 @@
         <v>SPA_ΑΠΟΚΛΕΙΣΜΟΣ</v>
       </c>
       <c r="B3" t="str">
-        <v>INTERXION</v>
+        <v>INTERXION;RAYCAP</v>
       </c>
       <c r="C3" t="str">
         <v>SPA customers που αγνοούνται (αρχή ονόματος, χωρισμένα με ;)</v>

--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -9464,7 +9464,7 @@
         <v>ΛΕΞΕΙΣ_ΑΚΡΟΔΕΚΤΗ</v>
       </c>
       <c r="B7" t="str">
-        <v>ΑΚΡΟΔΕΚΤΗΣ;ΚΩΣ ΠΡΕΣΑΣ</v>
+        <v>ΑΚΡΟΔΕΚΤ;ΚΩΣ</v>
       </c>
       <c r="C7" t="str">
         <v>Λέξεις περιγραφής για ακροδέκτες (κανόνας 2, πάντα MSRP, πάντα ανά τεμάχιο)</v>

--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -9397,7 +9397,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9472,40 +9472,51 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ΟΡΙΟ_ΠΑΝΩ</v>
+        <v>ΛΕΞΕΙΣ_RACK</v>
       </c>
       <c r="B8" t="str">
-        <v>5</v>
+        <v>RACK;FIBER RUNNER;PDU;CABINET;ΙΚΡΙΩΜΑ</v>
       </c>
       <c r="C8" t="str">
-        <v>Δ1: καθαρό νέο ÷ παλιό ≥ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+        <v>Λέξεις περιγραφής για rack/PDU/fiber runner (κανόνας 2β, πάντα MSRP — ειδικές τιμές έργων δεν γίνονται γενική τιμή)</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ΟΡΙΟ_ΚΑΤΩ</v>
+        <v>ΟΡΙΟ_ΠΑΝΩ</v>
       </c>
       <c r="B9" t="str">
-        <v>0,2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="str">
-        <v>Δ1: καθαρό νέο ÷ παλιό ≤ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+        <v>Δ1: καθαρό νέο ÷ παλιό ≥ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>ΟΡΙΟ_ΚΑΤΩ</v>
+      </c>
+      <c r="B10" t="str">
+        <v>0,2</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Δ1: καθαρό νέο ÷ παλιό ≤ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>ΚΟΣΤΟΣ_ΠΑΝΩ</v>
       </c>
-      <c r="B10" t="str">
+      <c r="B11" t="str">
         <v>1,25</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C11" t="str">
         <v>Δ5: SPA → MSRP με καθαρό ↑ ≥ αυτό → λίστα SPA→MSRP_ΚΟΣΤΟΣ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -8960,7 +8960,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9086,9 +9086,26 @@
         <v>Νίκος 09/2026</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>LCD1/0-14AF-X</v>
+      </c>
+      <c r="B9" t="str">
+        <v>ΑΚΡΟΔΕΚΤΗΣ ΜΗΧ.B.T.ΧΑΛΚΟΥ 50ΜΜ Φ6 90D 2Τ</v>
+      </c>
+      <c r="C9" t="str">
+        <v>πακέτο = 1</v>
+      </c>
+      <c r="D9" t="str">
+        <v>«2Τ» = 2 τρύπες, όχι 2 τεμάχια. Portal: 850,91/100 τεμ. = 8,51/τεμ.</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Report τιμολόγησης 20/10/2026</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -9414,7 +9414,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9500,40 +9500,51 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ΟΡΙΟ_ΠΑΝΩ</v>
+        <v>ΚΑΤΗΓΟΡΙΕΣ_RACK</v>
       </c>
       <c r="B9" t="str">
-        <v>5</v>
+        <v>FR;RK;CA</v>
       </c>
       <c r="C9" t="str">
-        <v>Δ1: καθαρό νέο ÷ παλιό ≥ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+        <v>Pricing Category του καταλόγου (1, 2 ή 3) που πάνε πάντα MSRP με τον κανόνα 2β. FR = fiber runner και σχάρες, RK = rack και παρελκόμενα, CA = cabinets</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>ΟΡΙΟ_ΚΑΤΩ</v>
+        <v>ΟΡΙΟ_ΠΑΝΩ</v>
       </c>
       <c r="B10" t="str">
-        <v>0,2</v>
+        <v>5</v>
       </c>
       <c r="C10" t="str">
-        <v>Δ1: καθαρό νέο ÷ παλιό ≤ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+        <v>Δ1: καθαρό νέο ÷ παλιό ≥ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
+        <v>ΟΡΙΟ_ΚΑΤΩ</v>
+      </c>
+      <c r="B11" t="str">
+        <v>0,2</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Δ1: καθαρό νέο ÷ παλιό ≤ αυτό → δεν γράφεται, ΓΙΑ_ΕΛΕΓΧΟ</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
         <v>ΚΟΣΤΟΣ_ΠΑΝΩ</v>
       </c>
-      <c r="B11" t="str">
+      <c r="B12" t="str">
         <v>1,25</v>
       </c>
-      <c r="C11" t="str">
+      <c r="C12" t="str">
         <v>Δ5: SPA → MSRP με καθαρό ↑ ≥ αυτό → λίστα SPA→MSRP_ΚΟΣΤΟΣ</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
+++ b/html/params/ΠΑΡΑΜΕΤΡΟΙ_v6.xlsx
@@ -8960,11 +8960,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Υπερισχύουν των πάντων. «Τι επιβάλλουμε» καταλαβαίνει: «πακέτο = N», «μονάδα = N», «ΑΠΟΔΟΧΗ ΑΠΟΚΛΙΣΗΣ» (περνά τη Δ1). Μπορείς να γράψεις πολλά χωρισμένα με ;</v>
+        <v>Υπερισχύουν των πάντων. «Τι επιβάλλουμε» καταλαβαίνει: «πακέτο = N», «μονάδα = N», «ΑΠΟΔΟΧΗ ΑΠΟΚΛΙΣΗΣ» (περνά τη Δ1), «ΠΑΝΤΑ MSRP» (ποτέ SPA πελάτη, όπως ο κανόνας 2β). Μπορείς να γράψεις πολλά χωρισμένα με ;</v>
       </c>
     </row>
     <row r="2">
@@ -9103,9 +9103,60 @@
         <v>Report τιμολόγησης 20/10/2026</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>SRB19BLY</v>
+      </c>
+      <c r="B10" t="str">
+        <v>ΠΙΣΩ ΟΔΗΓΟΣ ΚΑΛ.19''</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ΠΑΝΤΑ MSRP</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Παρελκόμενο rack: όχι SPA έργου πελάτη. Η κατηγορία καταλόγου (OU8/PC7/FB8) δεν είναι rack, γι'αυτό χρειάζεται εδώ.</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Νίκος 27/10/2026</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>GB4B1028TPI-1</v>
+      </c>
+      <c r="B11" t="str">
+        <v>ΜΠΑΡΑ ΓΕΙΩΣΗΣ ΔΙΑΤΡ 6,4X102Χ610MM</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ΠΑΝΤΑ MSRP</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Παρελκόμενο rack: όχι SPA έργου πελάτη. Η κατηγορία καταλόγου (OU8/PC7/FB8) δεν είναι rack, γι'αυτό χρειάζεται εδώ.</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Νίκος 27/10/2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>QAPP24BL</v>
+      </c>
+      <c r="B12" t="str">
+        <v>P.PANEL KENO ΓΩΝΙΑΚΟ QUICKNET</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ΠΑΝΤΑ MSRP</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Παρελκόμενο rack: όχι SPA έργου πελάτη. Η κατηγορία καταλόγου (OU8/PC7/FB8) δεν είναι rack, γι'αυτό χρειάζεται εδώ.</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Νίκος 27/10/2026</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E12"/>
   </ignoredErrors>
 </worksheet>
 </file>
